--- a/data/seed/portfolio/L-2025-7855/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-7855/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J163"/>
+  <dimension ref="A1:J171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -542,21 +542,21 @@
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>1580000</v>
+        <v>11732000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -566,77 +566,77 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Shartnoma №118/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №169/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11180000</v>
+        <v>21332000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>5114000</v>
+        <v>1165000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Mebel MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>272192769</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000294467879001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Shartnoma №220/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №185/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>16294000</v>
+        <v>22497000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2112000</v>
+        <v>3680000</v>
       </c>
       <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Samarqand Avto Ehtiyot MChJ</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>367580126</t>
+          <t>281673380</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000404159296001</t>
+          <t>20208000750676037001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -646,51 +646,51 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №35/26, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №70/26</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>14182000</v>
+        <v>18817000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>1525000</v>
+        <v>16352000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Samarqand Mato XK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>219276902</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000446787944001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №266/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6625</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>15707000</v>
+        <v>35169000</v>
       </c>
     </row>
     <row r="12">
@@ -702,21 +702,21 @@
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>2420000</v>
+        <v>15886000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -726,11 +726,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9793</t>
+          <t>Shartnoma №214/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>18127000</v>
+        <v>51055000</v>
       </c>
     </row>
     <row r="13">
@@ -742,35 +742,35 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>1318000</v>
+        <v>3239000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sharq Meva Eksport XK</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>278487208</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000381984080001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Shartnoma №63/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1004 06.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>19445000</v>
+        <v>54294000</v>
       </c>
     </row>
     <row r="14">
@@ -782,35 +782,35 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>771000</v>
+        <v>1949000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Kamalak Trans Servis AJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>373938933</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000556537489001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7581</t>
+          <t>Предоплата за товар по договору №86/26 от 06.07.2026</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>20216000</v>
+        <v>56243000</v>
       </c>
     </row>
     <row r="15">
@@ -820,18 +820,23 @@
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>8552000</v>
-      </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n">
+        <v>1550000</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Chirchiq Plastik XK</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -841,77 +846,77 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ish haqi, reestr №9511</t>
+          <t>Mahsulot uchun to'lov, shartnoma №167/26, QQS 12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>11664000</v>
+        <v>57793000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>839000</v>
+        <v>574000</v>
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sarbon Qurilish AJ</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>354419631</t>
+          <t>281673380</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000590602606001</t>
+          <t>20208000750676037001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №295/26, QQS bilan</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>10825000</v>
+        <v>57219000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>13013000</v>
+        <v>764000</v>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samarqand Avto Ehtiyot MChJ</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>367580126</t>
+          <t>281673380</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000404159296001</t>
+          <t>20208000750676037001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -921,237 +926,232 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №185/26</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №179/26, QQS bilan</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-2188000</v>
+        <v>56455000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n">
-        <v>4692000</v>
-      </c>
+      <c r="C18" s="2" t="n">
+        <v>1137000</v>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Denov Moy AJ</t>
+          <t>Jizzax Plastik AJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>265341321</t>
+          <t>384995022</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000287596351001</t>
+          <t>20208000098478302001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №198/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №28/26</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2504000</v>
+        <v>55318000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46216</v>
+        <v>46209</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n">
-        <v>30950000</v>
-      </c>
+      <c r="C19" s="2" t="n">
+        <v>1594000</v>
+      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>281673380</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000750676037001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №3479 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №278/26</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>33454000</v>
+        <v>53724000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46216</v>
+        <v>46209</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n">
-        <v>3404000</v>
-      </c>
+      <c r="C20" s="2" t="n">
+        <v>2478000</v>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sharq Meva Eksport XK</t>
+          <t>Jizzax Plastik AJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>278487208</t>
+          <t>384995022</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000381984080001</t>
+          <t>20208000098478302001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №4/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №91/26, QQS bilan</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>36858000</v>
+        <v>51246000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46216</v>
+        <v>46209</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n">
-        <v>2931000</v>
-      </c>
+      <c r="C21" s="2" t="n">
+        <v>8552000</v>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sharq Meva Eksport XK</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>278487208</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000381984080001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Shartnoma №269/26 bo'yicha oldindan to'lov</t>
+          <t>Iyun oyi uchun ish haqi, reestr №4183</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>39789000</v>
+        <v>42694000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46216</v>
+        <v>46210</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>860000</v>
+        <v>4223000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sharq Meva Eksport XK</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>278487208</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000381984080001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №273/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №134/26, НДС 12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>40649000</v>
+        <v>46917000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46217</v>
+        <v>46210</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n">
-        <v>1704000</v>
+        <v>1110000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1161,117 +1161,117 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №132/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7889 07.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>42353000</v>
+        <v>48027000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46217</v>
+        <v>46210</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>1166000</v>
+        <v>839000</v>
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bog'ishamol Qurilish AJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>236786866</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000484125638001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyun 2026</t>
+          <t>Ijara haqi iyul oyi uchun, shartnoma №41/25</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>41187000</v>
+        <v>47188000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46217</v>
+        <v>46210</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>1166000</v>
+        <v>957000</v>
       </c>
       <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Jizzax Plastik AJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>384995022</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000098478302001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>НАЛОГ НА ДОХОДЫ ФИЗИЧЕСКИХ ЛИЦ ЗА ИЮНЬ 2026 Г.</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №159/26</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>40021000</v>
+        <v>46231000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46218</v>
+        <v>46211</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>12693000</v>
+        <v>1251000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1281,37 +1281,37 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9270</t>
+          <t>Shartnoma №296/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>52714000</v>
+        <v>47482000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46218</v>
+        <v>46211</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>4936000</v>
+        <v>1209000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1321,632 +1321,637 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №7297 15.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №146/26, НДС 12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>57650000</v>
+        <v>48691000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46218</v>
+        <v>46211</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
-        <v>1809000</v>
-      </c>
+      <c r="C28" s="2" t="n">
+        <v>968000</v>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Omad Polimer XK</t>
+          <t>Jizzax Plastik AJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>211733766</t>
+          <t>384995022</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000116534456001</t>
+          <t>20208000098478302001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Shartnoma №41/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за материалы по дог. №91/26</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>59459000</v>
+        <v>47723000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46218</v>
+        <v>46211</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>12927000</v>
+        <v>1073000</v>
       </c>
       <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Samarqand Avto Ehtiyot MChJ</t>
+          <t>Jizzax Plastik AJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>367580126</t>
+          <t>384995022</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000404159296001</t>
+          <t>20208000098478302001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №8/26</t>
+          <t>Tovarlar uchun to'lov h/f №8063</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>46532000</v>
+        <v>46650000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46219</v>
+        <v>46212</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n">
-        <v>2936000</v>
-      </c>
+      <c r="C30" s="2" t="n">
+        <v>4701000</v>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sharq Meva Eksport XK</t>
+          <t>Jizzax Plastik AJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>278487208</t>
+          <t>384995022</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000381984080001</t>
+          <t>20208000098478302001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Shartnoma №94/26 bo'yicha oldindan to'lov</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №51/26, QQS bilan</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>49468000</v>
+        <v>41949000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46220</v>
+        <v>46217</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>7794000</v>
+        <v>7100000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Mebel MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>272192769</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000294467879001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Shartnoma №270/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9700</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>57262000</v>
+        <v>49049000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46220</v>
+        <v>46217</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n">
-        <v>1118000</v>
-      </c>
+      <c r="C32" s="2" t="n">
+        <v>1166000</v>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Mebel MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>272192769</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000294467879001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №209/26 от 17.07.2026</t>
+          <t>Уплата социального налога за июнь</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>58380000</v>
+        <v>47883000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46220</v>
+        <v>46217</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>12781000</v>
+        <v>1166000</v>
       </c>
       <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jizzax Un Mahsulotlari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>232430863</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000311343566001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4651</t>
+          <t>Jismoniy shaxslar daromad soli'i iyun 2026</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>45599000</v>
+        <v>46717000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46223</v>
+        <v>46218</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>1298000</v>
+        <v>2209000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sharq Meva Eksport XK</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>278487208</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000381984080001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №1/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №124</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>46897000</v>
+        <v>48926000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46223</v>
+        <v>46218</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n">
-        <v>1105000</v>
+        <v>1753000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Urganch Metall MChJ</t>
+          <t>Mehnat Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>397739389</t>
+          <t>241175414</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000385565374001</t>
+          <t>20208000526816847001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Shartnoma №170/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №293/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>48002000</v>
+        <v>50679000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46225</v>
+        <v>46218</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>1368000</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n">
+        <v>1275000</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chirchiq Plastik XK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимостьза июнь</t>
+          <t>Оплата за продукцию по договору №134/26, НДС 12%</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>46634000</v>
+        <v>51954000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46226</v>
+        <v>46218</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n">
-        <v>2349000</v>
-      </c>
+      <c r="C37" s="2" t="n">
+        <v>9503000</v>
+      </c>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Omad Polimer XK</t>
+          <t>Denov Plastik AJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>211733766</t>
+          <t>289660370</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000116534456001</t>
+          <t>20208000408388921001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №101/26 от 23.07.2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №70/26</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>48983000</v>
+        <v>42451000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46226</v>
+        <v>46218</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>40587000</v>
+        <v>20965000</v>
       </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ilhom Agro Servis MChJ</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>217019057</t>
+          <t>281673380</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000980491438001</t>
+          <t>20208000750676037001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №230/26</t>
+          <t>Оплата за упаковочные материалы, с/ №4938</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>8396000</v>
+        <v>21486000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46227</v>
+        <v>46219</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n">
-        <v>1903000</v>
+        <v>7278000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Mebel MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>272192769</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000294467879001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №105/26 от 24.07.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №363</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>10299000</v>
+        <v>28764000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46228</v>
+        <v>46219</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="D40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n">
+        <v>1844000</v>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-7855)</t>
+          <t>Chirchiq Farm Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>273376611</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>16307000255813237417</t>
+          <t>20208000653445609001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-7855 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8263 16.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>6099000</v>
+        <v>30608000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46230</v>
+        <v>46224</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n">
-        <v>3216000</v>
-      </c>
+      <c r="C41" s="2" t="n">
+        <v>1380000</v>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №96/26 от 27.07.2026</t>
+          <t>QQS iyun 2026 uchun</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>9315000</v>
+        <v>29228000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n">
-        <v>2382000</v>
-      </c>
+      <c r="C42" s="2" t="n">
+        <v>2255000</v>
+      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Denov Moy AJ</t>
+          <t>Jizzax Plastik AJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>265341321</t>
+          <t>384995022</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000287596351001</t>
+          <t>20208000098478302001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №167/26 от 27.07.2026</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №202/26, QQS bilan</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>11697000</v>
+        <v>26973000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>1124000</v>
+        <v>7715000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1956,317 +1961,312 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4121</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4411</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>12821000</v>
+        <v>34688000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n">
-        <v>1065000</v>
-      </c>
+      <c r="C44" s="2" t="n">
+        <v>524000</v>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Denov Moy AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>265341321</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000287596351001</t>
+          <t>20208000213661274001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3314 27.07.2026, QQS bilan</t>
+          <t>Elektr energiyasi uchun to'lov iyul</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>13886000</v>
+        <v>34164000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>524000</v>
+        <v>1491000</v>
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Denov Plastik AJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>289660370</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000569943694001</t>
+          <t>20208000408388921001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov iyul</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №225/26, QQS bilan</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>13362000</v>
+        <v>32673000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>3908000</v>
+        <v>23526000</v>
       </c>
       <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Samarqand Avto Ehtiyot MChJ</t>
+          <t>Jizzax Tikuv MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>367580126</t>
+          <t>298683970</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000404159296001</t>
+          <t>20208000385134509001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №268/26, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №28/26, QQS bilan</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>9454000</v>
+        <v>9147000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46231</v>
+        <v>46228</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>4365000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>341469288</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-7855)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>16307000255813237417</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №424</t>
+          <t>Kredit shartnomasi L-2025-7855 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>13819000</v>
+        <v>4947000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46232</v>
+        <v>46230</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>1937000</v>
+        <v>3909000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sharq Meva Eksport XK</t>
+          <t>Chirchiq Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>278487208</t>
+          <t>273376611</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000381984080001</t>
+          <t>20208000653445609001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №56/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №285/26 от 27.07.2026</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>15756000</v>
+        <v>8856000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>3104000</v>
+        <v>2166000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Chirchiq Plastik XK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4137</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7810 27.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>18860000</v>
+        <v>11022000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n">
-        <v>4725000</v>
-      </c>
-      <c r="D50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n">
+        <v>1887000</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Navoiy Plastik AJ</t>
+          <t>Chirchiq Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>281896603</t>
+          <t>273376611</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000074083889001</t>
+          <t>20208000653445609001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №12/26, QQS bilan</t>
+          <t>Tovar uchun to'lov, h/f №7329 27.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>14135000</v>
+        <v>12909000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n">
-        <v>1638000</v>
-      </c>
+      <c r="C51" s="2" t="n">
+        <v>2347000</v>
+      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Denov Moy AJ</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>265341321</t>
+          <t>281673380</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000287596351001</t>
+          <t>20208000750676037001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2276,72 +2276,77 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SHARTNOMA №157/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за упаковочные материалы, с/ф №4068</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>15773000</v>
+        <v>10562000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46234</v>
+        <v>46231</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>10980000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Sharq Avto Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>289053356</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000209673545001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Shartnoma №203/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>15473000</v>
+        <v>21542000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46234</v>
+        <v>46231</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>7733000</v>
+        <v>13769000</v>
       </c>
       <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Samarqand Avto Ehtiyot MChJ</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>367580126</t>
+          <t>281673380</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000404159296001</t>
+          <t>20208000750676037001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2351,37 +2356,37 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1867</t>
+          <t>Tovarlar uchun to'lov h/f №244</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>7740000</v>
+        <v>7773000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46237</v>
+        <v>46232</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>23552000</v>
+        <v>1638000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2391,37 +2396,37 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №35 ОТ 03.08.2026, В Т.Ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7113 29.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>31292000</v>
+        <v>9411000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46237</v>
+        <v>46233</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>2187000</v>
+        <v>2069000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2431,157 +2436,152 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №59/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №6113 30.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>33479000</v>
+        <v>11480000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46237</v>
+        <v>46233</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>608000</v>
+        <v>2050000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Mehnat Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>241175414</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000526816847001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Shartnoma №298/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartn. №280/26, QQS 12%</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>34087000</v>
+        <v>13530000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46237</v>
+        <v>46233</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>1413000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>1434000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ilhom Agro Servis MChJ</t>
+          <t>Chirchiq Plastik XK</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>217019057</t>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000980491438001</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №80/26</t>
+          <t>Shartnoma №288/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>32674000</v>
+        <v>14964000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46238</v>
+        <v>46233</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>1201000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>762000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>281673380</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000750676037001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Shartnoma №198/26 bo'yicha oldindan to'lov</t>
+          <t>Tovarlar uchun to'lov h/f №1162</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>33875000</v>
+        <v>14202000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46238</v>
+        <v>46234</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n">
-        <v>617000</v>
-      </c>
+      <c r="C59" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Denov Moy AJ</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>265341321</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000287596351001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2591,37 +2591,37 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №291/26, НДС 12%</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>34492000</v>
+        <v>13902000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46238</v>
+        <v>46234</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1226000</v>
+        <v>1121000</v>
       </c>
       <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Samarqand Avto Ehtiyot MChJ</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>367580126</t>
+          <t>281673380</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000404159296001</t>
+          <t>20208000750676037001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2631,312 +2631,317 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №235/26</t>
+          <t>Tovarlar uchun to'lov h/f №6177</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>33266000</v>
+        <v>12781000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46239</v>
+        <v>46234</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>17052000</v>
-      </c>
+      <c r="C61" s="2" t="n">
+        <v>3074000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Denov Moy AJ</t>
+          <t>Termiz Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>265341321</t>
+          <t>345929400</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000287596351001</t>
+          <t>20208000248969766001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4534 от 05.08.2026, в т.ч. НДС 12%</t>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №3/26, QQS BILAN</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>50318000</v>
+        <v>9707000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46240</v>
+        <v>46237</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n">
-        <v>8288000</v>
-      </c>
-      <c r="D62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n">
+        <v>6943000</v>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Namangan Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
+          <t>Mahsulot uchun to'lov, shartnoma №186/26, QQS 12%</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>42030000</v>
+        <v>16650000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46241</v>
+        <v>46237</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>876000</v>
+        <v>2065000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Urganch Metall MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>397739389</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000385565374001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Shartnoma №196/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №165/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>42906000</v>
+        <v>18715000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46241</v>
+        <v>46237</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>698000</v>
-      </c>
-      <c r="D64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n">
+        <v>939000</v>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ilhom Agro Servis MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>217019057</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000980491438001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №186/26, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5548</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>42208000</v>
+        <v>19654000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46241</v>
+        <v>46237</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>813000</v>
+        <v>16547000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sarbon Qurilish AJ</t>
+          <t>Jizzax Tikuv MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>354419631</t>
+          <t>298683970</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000590602606001</t>
+          <t>20208000385134509001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Арендная плата за август 2026 г. по договору №7/20</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №93/26</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>41395000</v>
+        <v>3107000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>1215000</v>
+        <v>2287000</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Samarqand Avto Ehtiyot MChJ</t>
+          <t>Jizzax Plastik AJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>367580126</t>
+          <t>384995022</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000404159296001</t>
+          <t>20208000098478302001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №123/26</t>
+          <t>Предоплата за материалы по договору №69/26</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>40180000</v>
+        <v>820000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46244</v>
+        <v>46239</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n">
-        <v>1567000</v>
+        <v>4943000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sharq Meva Eksport XK</t>
+          <t>Chirchiq Plastik XK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>278487208</t>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000381984080001</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №281/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3381</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>41747000</v>
+        <v>5763000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46244</v>
+        <v>46239</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>1232000</v>
+        <v>969000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Omad Polimer XK</t>
+          <t>Chirchiq Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>211733766</t>
+          <t>273376611</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000116534456001</t>
+          <t>20208000653445609001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2946,117 +2951,112 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №176/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №292 05.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>42979000</v>
+        <v>6732000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46244</v>
+        <v>46239</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n">
-        <v>742000</v>
-      </c>
+      <c r="C69" s="2" t="n">
+        <v>8288000</v>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>341469288</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4428 10.08.2026, QQS bilan</t>
+          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №4288</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>43721000</v>
+        <v>-1556000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46245</v>
+        <v>46240</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>2048000</v>
-      </c>
-      <c r="D70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n">
+        <v>3623000</v>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Samarqand Avto Ehtiyot MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>367580126</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000404159296001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №7830</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3399 06.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>41673000</v>
+        <v>2067000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46246</v>
+        <v>46240</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>2947000</v>
+        <v>2429000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3066,197 +3066,197 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2449</t>
+          <t>Tovar uchun to'lov, h/f №415 06.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>44620000</v>
+        <v>4496000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46246</v>
+        <v>46240</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>2025000</v>
+        <v>1104000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Chirchiq Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>273376611</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000653445609001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SHARTNOMA №109/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6662</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>46645000</v>
+        <v>5600000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46246</v>
+        <v>46241</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>1005000</v>
+        <v>4396000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Mebel MChJ</t>
+          <t>Sharq Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>272192769</t>
+          <t>289053356</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000294467879001</t>
+          <t>20208000209673545001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, sharnoma №125/26, QQS 12%</t>
+          <t>Оплата по счет-фактре №1196 за поставленный товар</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>47650000</v>
+        <v>9996000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>902000</v>
+        <v>2262000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sharq Meva Eksport XK</t>
+          <t>Chirchiq Plastik XK</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>278487208</t>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000381984080001</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №100/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №966 10.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>48552000</v>
+        <v>12258000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>1205000</v>
-      </c>
-      <c r="D75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n">
+        <v>1887000</v>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Samarqand Avto Ehtiyot MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>367580126</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000404159296001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №30/26, QQS bilan</t>
+          <t>Tovar uchun to'lov, h/f №1857 10.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>47347000</v>
+        <v>14145000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="n">
-        <v>6714000</v>
+        <v>1173000</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3266,37 +3266,37 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №186/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №23/26, QQS 12%</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>54061000</v>
+        <v>15318000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>666000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>813000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Bog'ishamol Qurilish AJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>236786866</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000484125638001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3306,336 +3306,336 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №133/26, QQS 12%</t>
+          <t>Ijara haqi avgust oyi uchun, shartnoma №41/25</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>54727000</v>
+        <v>14505000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>5637000</v>
+        <v>2847000</v>
       </c>
       <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Qarshi Qog'oz MChJ</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>394890533</t>
+          <t>281673380</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000672096735001</t>
+          <t>20208000750676037001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №268/26, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №215/26, QQS bilan</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>49090000</v>
+        <v>11658000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46248</v>
+        <v>46244</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>1843000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>6560000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Jizzax Plastik AJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>384995022</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000098478302001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №278/26, QQS 12%</t>
+          <t>Materiallar uchun oldidan to'lov, shartnoma №95/26</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>50933000</v>
+        <v>5098000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46248</v>
+        <v>46245</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>930000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>4468000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Denov Plastik AJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>289660370</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000408388921001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №278/26 от 14.08.2026</t>
+          <t>Tovarlar uchun to'lov h/f №422</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>51863000</v>
+        <v>630000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46251</v>
+        <v>46246</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>1630000</v>
+        <v>3881000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Omad Polimer XK</t>
+          <t>Chirchiq Plastik XK</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>211733766</t>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000116534456001</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №60/26, QQS 12%</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №1150 12.08.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>53493000</v>
+        <v>4511000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46251</v>
+        <v>46246</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>1221000</v>
+        <v>1862000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Omad Polimer XK</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>211733766</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000116534456001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №155/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8767</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>54714000</v>
+        <v>6373000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46251</v>
+        <v>46246</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n">
-        <v>901000</v>
-      </c>
+      <c r="C83" s="2" t="n">
+        <v>2671000</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Mebel MChJ</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>272192769</t>
+          <t>281673380</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000294467879001</t>
+          <t>20208000750676037001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №250/26, НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №5346</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>55615000</v>
+        <v>3702000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46251</v>
+        <v>46246</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n">
-        <v>735000</v>
-      </c>
+      <c r="C84" s="2" t="n">
+        <v>8076000</v>
+      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Denov Moy AJ</t>
+          <t>Jizzax Plastik AJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>265341321</t>
+          <t>384995022</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000287596351001</t>
+          <t>20208000098478302001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №206/26, QQS 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №190/26</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>56350000</v>
+        <v>-4374000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>568000</v>
+        <v>1835000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sharq Meva Eksport XK</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>278487208</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000381984080001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №463 17.08.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3460 14.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>56918000</v>
+        <v>-2539000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
@@ -3666,16 +3666,16 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Социальный налог за июль 2026 г.</t>
+          <t>Ijtimoiy soliq iyul 2026</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>55788000</v>
+        <v>-3669000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
@@ -3706,11 +3706,11 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>JShDS iyul oi uchun</t>
+          <t>Налог на доходы физических лиц за июль 2026 г.</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>54658000</v>
+        <v>-4799000</v>
       </c>
     </row>
     <row r="88">
@@ -3720,37 +3720,37 @@
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>1260000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>6888000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Samarqand Avto Ehtiyot MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>367580126</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000404159296001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №243/26, QQS bilan</t>
+          <t>SHARTNOMA №237/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>53398000</v>
+        <v>2089000</v>
       </c>
     </row>
     <row r="89">
@@ -3760,423 +3760,423 @@
       <c r="B89" t="n">
         <v>181</v>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>2631000</v>
-      </c>
-      <c r="D89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n">
+        <v>5736000</v>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Omad Mato MChJ</t>
+          <t>Kamalak Trans Servis AJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>323678686</t>
+          <t>373938933</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000648412563001</t>
+          <t>20208000556537489001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №161/26</t>
+          <t>Shartnoma №186/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>50767000</v>
+        <v>7825000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>863000</v>
+        <v>1776000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Denov Moy AJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>265341321</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000287596351001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №178/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5647 17.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>51630000</v>
+        <v>9601000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>787000</v>
+        <v>1466000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sharq Meva Eksport XK</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>278487208</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000381984080001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №270/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2611</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>52417000</v>
+        <v>11067000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46254</v>
+        <v>46251</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="n">
-        <v>5274000</v>
+        <v>1174000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sharq Meva Eksport XK</t>
+          <t>Yangi Hayot Poligraf MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>278487208</t>
+          <t>243086383</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000381984080001</t>
+          <t>20208000134356696001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6900 20.08.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №7400 за поставленный товар</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>57691000</v>
+        <v>12241000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46254</v>
+        <v>46251</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
       <c r="C93" s="2" t="n"/>
       <c r="D93" s="2" t="n">
-        <v>2625000</v>
+        <v>952000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sharq Meva Eksport XK</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>278487208</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000381984080001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7716</t>
+          <t>Оплата за продукцию по дог. №96/26, НДС 12%</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>60316000</v>
+        <v>13193000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46255</v>
+        <v>46252</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>1663000</v>
+        <v>1179000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tong Polimer MChJ</t>
+          <t>Chirchiq Plastik XK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>364411754</t>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000415268168001</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Shartnoma №165/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №139/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>61979000</v>
+        <v>14372000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46255</v>
+        <v>46252</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>1018000</v>
+        <v>746000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sharq Meva Eksport XK</t>
+          <t>Chirchiq Plastik XK</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>278487208</t>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000381984080001</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №207/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №131/26, QQS 12%</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>62997000</v>
+        <v>15118000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46255</v>
+        <v>46252</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n">
-        <v>777000</v>
-      </c>
+      <c r="C96" s="2" t="n">
+        <v>30753000</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Denov Plastik AJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>289660370</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000408388921001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5582</t>
+          <t>Tovarlar uchun to'lov h/f №6771</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>63774000</v>
+        <v>-15635000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n">
+        <v>2321000</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
+          <t>Shartnoma №251/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>62424000</v>
+        <v>-13314000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>15690000</v>
+        <v>2226000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Kamalak Trans Servis AJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>373938933</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000556537489001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №290/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №218/26, QQS 12%</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>78114000</v>
+        <v>-11088000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>3471000</v>
+        <v>5939000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4186,37 +4186,37 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №75/26, QQS 12%</t>
+          <t>Shartnoma №62/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>81585000</v>
+        <v>-5149000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>1996000</v>
+        <v>4272000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4226,51 +4226,51 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1095</t>
+          <t>Shartnoma №110/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>83581000</v>
+        <v>-877000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>891000</v>
+        <v>1238000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Denov Moy AJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>265341321</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000287596351001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3898</t>
+          <t>Mahsulot uchun to'lov, shartnoma №112/26, QQS 12%</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>84472000</v>
+        <v>361000</v>
       </c>
     </row>
     <row r="102">
@@ -4282,21 +4282,21 @@
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>846000</v>
+        <v>3804000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4306,11 +4306,11 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Shartnoma №257/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №100/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>85318000</v>
+        <v>4165000</v>
       </c>
     </row>
     <row r="103">
@@ -4320,77 +4320,77 @@
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>49930000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>1569000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Jizzax Un Mahsulotlari MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>232430863</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000311343566001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5644</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4161</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>35388000</v>
+        <v>5734000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n">
-        <v>2889000</v>
-      </c>
+      <c r="C104" s="2" t="n">
+        <v>1356000</v>
+      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Mebel MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>272192769</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000294467879001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №14/26, НДС 12%</t>
+          <t>НДС за июль 2026 г.</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>38277000</v>
+        <v>4378000</v>
       </c>
     </row>
     <row r="105">
@@ -4400,23 +4400,23 @@
       <c r="B105" t="n">
         <v>197</v>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>508000</v>
-      </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>1274000</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000569943694001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4426,11 +4426,11 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1837</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>37769000</v>
+        <v>5652000</v>
       </c>
     </row>
     <row r="106">
@@ -4465,47 +4465,47 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>33569000</v>
+        <v>1452000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n">
-        <v>752000</v>
-      </c>
+      <c r="C107" s="2" t="n">
+        <v>15169000</v>
+      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Mebel MChJ</t>
+          <t>Denov Plastik AJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>272192769</t>
+          <t>289660370</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000294467879001</t>
+          <t>20208000408388921001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №22/26, QQS 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №7534</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>34321000</v>
+        <v>-13717000</v>
       </c>
     </row>
     <row r="108">
@@ -4517,35 +4517,35 @@
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>709000</v>
+        <v>2671000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Chirchiq Plastik XK</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №9584 26.08.2026, QQS BILAN</t>
+          <t>TOVAR UCHUN TO'LOV, H/F №9740 26.08.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>35030000</v>
+        <v>-11046000</v>
       </c>
     </row>
     <row r="109">
@@ -4555,23 +4555,23 @@
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>25198000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>1740000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Samarqand Avto Ehtiyot MChJ</t>
+          <t>Samarqand Mato XK</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>367580126</t>
+          <t>219276902</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000404159296001</t>
+          <t>20208000446787944001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4581,37 +4581,37 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №187/26, QQS bilan</t>
+          <t>Предоплата за товар по дог. №79/26 от 26.08.2026</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>9832000</v>
+        <v>-9306000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
-      <c r="C110" s="2" t="n">
-        <v>872000</v>
-      </c>
-      <c r="D110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n">
+        <v>1156000</v>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Samarqand Avto Ehtiyot MChJ</t>
+          <t>Chirchiq Plastik XK</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>367580126</t>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000404159296001</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4621,37 +4621,37 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6727</t>
+          <t>Shartnoma №157/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>8960000</v>
+        <v>-8150000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46265</v>
+        <v>46261</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>552000</v>
+        <v>2952000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4661,72 +4661,77 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №123/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №182/26, QQS 12%</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>9512000</v>
+        <v>-5198000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46265</v>
+        <v>46261</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>300000</v>
+        <v>508000</v>
       </c>
       <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000213661274001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>9212000</v>
+        <v>-5706000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46265</v>
+        <v>46261</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>663000</v>
+        <v>3611000</v>
       </c>
       <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Samarqand Avto Ehtiyot MChJ</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>367580126</t>
+          <t>281673380</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000404159296001</t>
+          <t>20208000750676037001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4736,157 +4741,157 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5782</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №86/26</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>8549000</v>
+        <v>-9317000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46266</v>
+        <v>46262</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>9663000</v>
+        <v>10802000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Chirchiq Plastik XK</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №292/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №29/26, QQS 12%</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>18212000</v>
+        <v>1485000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46266</v>
+        <v>46262</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n"/>
       <c r="D115" s="2" t="n">
-        <v>862000</v>
+        <v>7131000</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sharq Meva Eksport XK</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>278487208</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000381984080001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisb-faktura №6602 01.09.2026, QQS bilan</t>
+          <t>Shartnoma №184/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>19074000</v>
+        <v>8616000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>5176000</v>
-      </c>
-      <c r="D116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n">
+        <v>2106000</v>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Jizzax Un Mahsulotlari MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>232430863</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000311343566001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3580</t>
+          <t>Shartnoma №149/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>13898000</v>
+        <v>10722000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>2657000</v>
+        <v>1583000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Denov Moy AJ</t>
+          <t>Chirchiq Plastik XK</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>265341321</t>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000287596351001</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4896,77 +4901,72 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Shartnoma №186/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, h/f №5857 31.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>16555000</v>
+        <v>12305000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n">
-        <v>1482000</v>
-      </c>
+      <c r="C118" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>272192769</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000294467879001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>SHARTNOMA №278/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>18037000</v>
+        <v>12005000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46269</v>
+        <v>46266</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>1569000</v>
+        <v>5446000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Omad Polimer XK</t>
+          <t>Chirchiq Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>211733766</t>
+          <t>273376611</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000116534456001</t>
+          <t>20208000653445609001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -4976,131 +4976,131 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №3792 04.09.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9604 01.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>19606000</v>
+        <v>17451000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46272</v>
+        <v>46268</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>3400000</v>
+        <v>1420000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Chirchiq Plastik XK</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №203/26, QQS 12%</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №120/26, QQS 12%</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>23006000</v>
+        <v>18871000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46272</v>
+        <v>46269</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="n">
-        <v>2048000</v>
+        <v>3483000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Mebel MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>272192769</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000294467879001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №216/26, НДС 12%</t>
+          <t>Предоплата за товар по дог. №287/26 от 04.09.2026</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>25054000</v>
+        <v>22354000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46272</v>
+        <v>46269</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n">
-        <v>1704000</v>
-      </c>
+      <c r="C122" s="2" t="n">
+        <v>2343000</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Urganch Metall MChJ</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>397739389</t>
+          <t>281673380</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000385565374001</t>
+          <t>20208000750676037001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №700 07.09.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №7409</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>26758000</v>
+        <v>20011000</v>
       </c>
     </row>
     <row r="123">
@@ -5110,192 +5110,192 @@
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>8593000</v>
-      </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n">
+        <v>2826000</v>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Sharq Avto Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>289053356</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000209673545001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ish haqi, reestr №1217</t>
+          <t>Оплата за продукцию по договору №271/26, НДС 12%</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>18165000</v>
+        <v>22837000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
-      <c r="C124" s="2" t="n">
-        <v>7368000</v>
-      </c>
-      <c r="D124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n">
+        <v>900000</v>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Navoiy Plastik AJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>281896603</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000074083889001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №25/26</t>
+          <t>Предоплата за товар по договору №261/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>10797000</v>
+        <v>23737000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46274</v>
+        <v>46272</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>843000</v>
+        <v>8593000</v>
       </c>
       <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sarbon Qurilish AJ</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>354419631</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000590602606001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Ijara haqi sentyabr oyi uchun, shartnoma №7/20</t>
+          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>9954000</v>
+        <v>15144000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46275</v>
+        <v>46272</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>2290000</v>
-      </c>
+      <c r="C126" s="2" t="n">
+        <v>14046000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Tong Polimer MChJ</t>
+          <t>Jizzax Plastik AJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>364411754</t>
+          <t>384995022</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000415268168001</t>
+          <t>20208000098478302001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3886</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №77/26</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>12244000</v>
+        <v>1098000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n">
-        <v>1213000</v>
-      </c>
+      <c r="C127" s="2" t="n">
+        <v>843000</v>
+      </c>
+      <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Mebel MChJ</t>
+          <t>Bog'ishamol Qurilish AJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>272192769</t>
+          <t>236786866</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000294467879001</t>
+          <t>20208000484125638001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №169/26 от 10.09.2026</t>
+          <t>Ijara haqi sentyabr oyi uchun, shartn. №41/25</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>13457000</v>
+        <v>255000</v>
       </c>
     </row>
     <row r="128">
@@ -5307,21 +5307,21 @@
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>871000</v>
+        <v>1283000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5331,37 +5331,37 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4399 10.09.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №97/26, QQS 12%</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>14328000</v>
+        <v>1538000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>1273000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Qarshi Qog'oz MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>394890533</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000672096735001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5371,37 +5371,37 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №274/26, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4240</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>8328000</v>
+        <v>2811000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>5847000</v>
+        <v>916000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5411,11 +5411,11 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №4689 14.09.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, h/f №9427 10.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>14175000</v>
+        <v>3727000</v>
       </c>
     </row>
     <row r="131">
@@ -5427,35 +5427,35 @@
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>4781000</v>
+        <v>1583000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Chirchiq Plastik XK</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Shartnoma №220/26 bo'yicha oldindan to'lov</t>
+          <t>SHARTNOMA №57/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>18956000</v>
+        <v>5310000</v>
       </c>
     </row>
     <row r="132">
@@ -5467,35 +5467,35 @@
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>3831000</v>
+        <v>1235000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Omad Polimer XK</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>211733766</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000116534456001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3641</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7623 14.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>22787000</v>
+        <v>6545000</v>
       </c>
     </row>
     <row r="133">
@@ -5507,21 +5507,21 @@
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>3198000</v>
+        <v>927000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Denov Moy AJ</t>
+          <t>Chirchiq Plastik XK</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>265341321</t>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000287596351001</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5531,11 +5531,11 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №58/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2132</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>25985000</v>
+        <v>7472000</v>
       </c>
     </row>
     <row r="134">
@@ -5545,37 +5545,37 @@
       <c r="B134" t="n">
         <v>226</v>
       </c>
-      <c r="C134" s="2" t="n"/>
-      <c r="D134" s="2" t="n">
-        <v>1773000</v>
-      </c>
+      <c r="C134" s="2" t="n">
+        <v>2359000</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Omad Polimer XK</t>
+          <t>Denov Plastik AJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>211733766</t>
+          <t>289660370</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000116534456001</t>
+          <t>20208000408388921001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Shartnoma №139/26 bo'yicha oldindan t'lov</t>
+          <t>Tovarlar uchun to'lov h/f №8838</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>27758000</v>
+        <v>5113000</v>
       </c>
     </row>
     <row r="135">
@@ -5585,37 +5585,37 @@
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>1206000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>2761000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Tong Polimer MChJ</t>
+          <t>Termiz Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>364411754</t>
+          <t>345929400</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000415268168001</t>
+          <t>20208000248969766001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7169</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №107/26</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>28964000</v>
+        <v>2352000</v>
       </c>
     </row>
     <row r="136">
@@ -5626,22 +5626,22 @@
         <v>228</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>4152000</v>
+        <v>7082000</v>
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Samarqand Avto Ehtiyot MChJ</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>367580126</t>
+          <t>281673380</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000404159296001</t>
+          <t>20208000750676037001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5651,11 +5651,11 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №259/26, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №114/26, QQS bilan</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>24812000</v>
+        <v>-4730000</v>
       </c>
     </row>
     <row r="137">
@@ -5667,21 +5667,21 @@
       </c>
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="n">
-        <v>2000000</v>
+        <v>1669000</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Denov Moy AJ</t>
+          <t>Samarqand Mato XK</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>265341321</t>
+          <t>219276902</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000287596351001</t>
+          <t>20208000446787944001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5691,37 +5691,37 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Shartnoma №22/26 bo'yicha oldindan to'lov</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №7577 ОТ 15.09.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>26812000</v>
+        <v>-3061000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>1428000</v>
+        <v>10276000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5731,11 +5731,11 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8813 от 15.09.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №23/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>28240000</v>
+        <v>7215000</v>
       </c>
     </row>
     <row r="139">
@@ -5745,37 +5745,37 @@
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n">
-        <v>1541000</v>
-      </c>
+      <c r="C139" s="2" t="n">
+        <v>1172000</v>
+      </c>
+      <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sharq Meva Eksport XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>278487208</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000381984080001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №234/26, QQS 12%</t>
+          <t>Ijtimoiy soliq avgust 2026</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>29781000</v>
+        <v>6043000</v>
       </c>
     </row>
     <row r="140">
@@ -5811,91 +5811,91 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq avgust 2026</t>
+          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>28609000</v>
+        <v>4871000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n">
-        <v>1172000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n">
+        <v>6393000</v>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chirchiq Plastik XK</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9002 17.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>27437000</v>
+        <v>11264000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
-      <c r="C142" s="2" t="n">
-        <v>7332000</v>
-      </c>
-      <c r="D142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n">
+        <v>5253000</v>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Samarqand Avto Ehtiyot MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>367580126</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000404159296001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №4454</t>
+          <t>Shartnoma №159/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>20105000</v>
+        <v>16517000</v>
       </c>
     </row>
     <row r="143">
@@ -5907,21 +5907,21 @@
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>4940000</v>
+        <v>2356000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5931,37 +5931,37 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Shartnoma №200/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №28/26, QQS 12%</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>25045000</v>
+        <v>18873000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="n">
-        <v>6012000</v>
+        <v>2127000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -5971,77 +5971,77 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8741</t>
+          <t>Mahsulot uchun to'lov, shartnoma №203/26, QQS 12%</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>31057000</v>
+        <v>21000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>5861000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>7177000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Denov Moy AJ</t>
+          <t>Jizzax Plastik AJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>265341321</t>
+          <t>384995022</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000287596351001</t>
+          <t>20208000098478302001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №4969</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №99/26</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>36918000</v>
+        <v>13823000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="n">
-        <v>2793000</v>
+        <v>5007000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6051,11 +6051,11 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Shartnoma №229/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №149/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>39711000</v>
+        <v>18830000</v>
       </c>
     </row>
     <row r="147">
@@ -6065,143 +6065,143 @@
       <c r="B147" t="n">
         <v>239</v>
       </c>
-      <c r="C147" s="2" t="n">
-        <v>43034000</v>
-      </c>
-      <c r="D147" s="2" t="n"/>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n">
+        <v>27530000</v>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Qarshi Qog'oz MChJ</t>
+          <t>Chirchiq Plastik XK</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>394890533</t>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000672096735001</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №259/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8788</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>-3323000</v>
+        <v>46360000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
       <c r="C148" s="2" t="n"/>
       <c r="D148" s="2" t="n">
-        <v>25888000</v>
+        <v>2753000</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Sharq Meva Eksport XK</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>278487208</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000381984080001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, H/F №3915 22.09.2026, QQS BILAN</t>
+          <t>Shartnoma №48/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>22565000</v>
+        <v>49113000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
-      <c r="C149" s="2" t="n">
-        <v>1412000</v>
-      </c>
-      <c r="D149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n">
+        <v>1809000</v>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>QQS avgust 2026 uchun</t>
+          <t>SHARTNOMA №278/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>21153000</v>
+        <v>50922000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
       <c r="C150" s="2" t="n"/>
       <c r="D150" s="2" t="n">
-        <v>1335000</v>
+        <v>1552000</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Denov Moy AJ</t>
+          <t>Samarqand Mato XK</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>265341321</t>
+          <t>219276902</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000287596351001</t>
+          <t>20208000446787944001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6211,72 +6211,77 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №104/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7200 21.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>22488000</v>
+        <v>52474000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
-      <c r="C151" s="2" t="n">
-        <v>527000</v>
-      </c>
-      <c r="D151" s="2" t="n"/>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n">
+        <v>1524000</v>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Chirchiq Plastik XK</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000569943694001</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Yetkazilan tovar uchun to'lov h/f №8852</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>21961000</v>
+        <v>53998000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
-      <c r="C152" s="2" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="D152" s="2" t="n"/>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="2" t="n">
+        <v>6233000</v>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-7855)</t>
+          <t>Chirchiq Plastik XK</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>348720883</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>16307000255813237417</t>
+          <t>20208000198408042001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6286,391 +6291,706 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-7855 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6937 22.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>17761000</v>
+        <v>60231000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n">
-        <v>9386000</v>
-      </c>
+      <c r="C153" s="2" t="n">
+        <v>1358000</v>
+      </c>
+      <c r="D153" s="2" t="n"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Sharq Meva Eksport XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>278487208</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000381984080001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8256 от 28.09.2026, в т.ч. НДС 12%</t>
+          <t>QQS avgust 2026 uchun</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>27147000</v>
+        <v>58873000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n">
-        <v>5121000</v>
-      </c>
+      <c r="C154" s="2" t="n">
+        <v>2075000</v>
+      </c>
+      <c r="D154" s="2" t="n"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>281673380</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000750676037001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №222/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №27/26</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>32268000</v>
+        <v>56798000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
       <c r="C155" s="2" t="n"/>
       <c r="D155" s="2" t="n">
-        <v>1915000</v>
+        <v>3616000</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Omad Polimer XK</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>211733766</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000116534456001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7721</t>
+          <t>Shartnoma №251/26 bo'yica oldindan to'lov</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>34183000</v>
+        <v>60414000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="B156" t="n">
         <v>248</v>
       </c>
-      <c r="C156" s="2" t="n"/>
-      <c r="D156" s="2" t="n">
-        <v>1071000</v>
-      </c>
+      <c r="C156" s="2" t="n">
+        <v>527000</v>
+      </c>
+      <c r="D156" s="2" t="n"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>341469288</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000764099258001</t>
+          <t>20208000213661274001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3259 28.09.2026, QQS bilan</t>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>35254000</v>
+        <v>59887000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="B157" t="n">
         <v>249</v>
       </c>
-      <c r="C157" s="2" t="n">
-        <v>4437000</v>
-      </c>
-      <c r="D157" s="2" t="n"/>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>4075000</v>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Samarqand Avto Ehtiyot MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>367580126</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000404159296001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №86/26, QQS bilan</t>
+          <t>Shartnoma №133/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>30817000</v>
+        <v>63962000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="B158" t="n">
         <v>250</v>
       </c>
-      <c r="C158" s="2" t="n">
-        <v>5156000</v>
-      </c>
-      <c r="D158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>2037000</v>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Buxoro Metall MChJ</t>
+          <t>Sharq Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>252816733</t>
+          <t>289053356</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000087506760001</t>
+          <t>20208000209673545001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTN. №141/26, QQS BILAN</t>
+          <t>Оплата за продукцию по договору №135/26, НДС 12%</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>25661000</v>
+        <v>65999000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="B159" t="n">
         <v>251</v>
       </c>
       <c r="C159" s="2" t="n">
-        <v>8552000</v>
+        <v>4200000</v>
       </c>
       <c r="D159" s="2" t="n"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Navoiy Plastik AJ</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>281896603</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-7855)</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000074083889001</t>
+          <t>16307000255813237417</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2474</t>
+          <t>Kredit shartnomasi L-2025-7855 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>17109000</v>
+        <v>61799000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="B160" t="n">
         <v>252</v>
       </c>
-      <c r="C160" s="2" t="n">
-        <v>6809000</v>
-      </c>
-      <c r="D160" s="2" t="n"/>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n">
+        <v>2203000</v>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Jizzax Un Mahsulotlari MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>232430863</t>
+          <t>246928867</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000311343566001</t>
+          <t>20208000409925851001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №218/26</t>
+          <t>Оплата за продукцию по договору №64/26, НДС 12%</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>10300000</v>
+        <v>64002000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="B161" t="n">
         <v>253</v>
       </c>
-      <c r="C161" s="2" t="n">
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n">
+        <v>2178000</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Sharq Avto Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>289053356</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>20208000209673545001</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №428 28.09.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>66180000</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B162" t="n">
+        <v>254</v>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>3838000</v>
+      </c>
+      <c r="D162" s="2" t="n"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Jizzax Plastik AJ</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>384995022</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20208000098478302001</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>TOVARLAR UCHUN TO'LOV H/F №4297</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>62342000</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B163" t="n">
+        <v>255</v>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>4684000</v>
+      </c>
+      <c r="D163" s="2" t="n"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Tong Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>281673380</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000750676037001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartnoma №101/26, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>57658000</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B164" t="n">
+        <v>256</v>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>5080000</v>
+      </c>
+      <c r="D164" s="2" t="n"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Jizzax Plastik AJ</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>384995022</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20208000098478302001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно с/ф №7144</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>52578000</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B165" t="n">
+        <v>257</v>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>5998000</v>
+      </c>
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Jizzax Plastik AJ</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>384995022</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>20208000098478302001</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №295/26</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>46580000</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B166" t="n">
+        <v>258</v>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>7838000</v>
+      </c>
+      <c r="D166" s="2" t="n"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Tong Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>281673380</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20208000750676037001</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Оплата за упаковочные материалы, с/ф №6609</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>38742000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B167" t="n">
+        <v>259</v>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>31688000</v>
+      </c>
+      <c r="D167" s="2" t="n"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Tong Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>281673380</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>20208000750676037001</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartnoma №22/26, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>7054000</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B168" t="n">
+        <v>260</v>
+      </c>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n">
+        <v>3246000</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Namangan Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>246928867</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>20208000409925851001</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №114/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>10300000</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B169" t="n">
+        <v>261</v>
+      </c>
+      <c r="C169" s="2" t="n">
         <v>300000</v>
       </c>
-      <c r="D161" s="2" t="n"/>
-      <c r="E161" t="inlineStr">
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" t="inlineStr">
         <is>
           <t>Sarbon Moliya Bank</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
+      <c r="G169" t="inlineStr">
         <is>
           <t>45994000900000001001</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
+      <c r="H169" t="inlineStr">
         <is>
           <t>00962</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Bank xizmati uchun komissiya</t>
-        </is>
-      </c>
-      <c r="J161" s="2" t="n">
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Комиссия за перевод</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
         <v>10000000</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
+    <row r="170">
+      <c r="A170" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C162" s="4" t="n">
-        <v>343851000</v>
-      </c>
-      <c r="D162" s="4" t="n">
-        <v>344251000</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
+      <c r="C170" s="4" t="n">
+        <v>340714000</v>
+      </c>
+      <c r="D170" s="4" t="n">
+        <v>341114000</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C163" s="4" t="n">
+      <c r="C171" s="4" t="n">
         <v>10000000</v>
       </c>
-      <c r="D163" s="4" t="n"/>
+      <c r="D171" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
